--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260804.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260804.xlsx
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>1,290,404</t>
+          <t>89,309,324</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>89,309,324</t>
+          <t>1,290,404</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>26,709,548</t>
+          <t>45,786,183</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>45,786,183</t>
+          <t>26,709,548</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>72,395,414</t>
+          <t>368,599,159</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>368,599,159</t>
+          <t>72,395,414</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>26,730,989</t>
+          <t>245,470,189</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>245,470,189</t>
+          <t>26,730,989</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>25,515,120</t>
+          <t>5,015,090</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>5,015,090</t>
+          <t>25,515,120</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
